--- a/data/trans_orig/IQ2605_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2605_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28659</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>41761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29356</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46146</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43781</t>
+          <t>44308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68144</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92790</t>
+          <t>91733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85576</t>
+          <t>86201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113067</t>
+          <t>114289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159901</t>
+          <t>158323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197893</t>
+          <t>198058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125483</t>
+          <t>126051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156750</t>
+          <t>157367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124234</t>
+          <t>124375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156562</t>
+          <t>156507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260322</t>
+          <t>258118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304666</t>
+          <t>307298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141289</t>
+          <t>139629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172679</t>
+          <t>172872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167147</t>
+          <t>165138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>199054</t>
+          <t>200249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>318476</t>
+          <t>317072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>363335</t>
+          <t>362978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34621</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>31784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>51238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19964</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>26483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>45757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51485</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75772</t>
+          <t>75261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101414</t>
+          <t>101941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>58125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39070</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57643</t>
+          <t>57331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84754</t>
+          <t>82419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54650</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75290</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>63343</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103174</t>
+          <t>104609</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131901</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164474</t>
+          <t>163087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152860</t>
+          <t>153880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187095</t>
+          <t>190603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>291072</t>
+          <t>294157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340788</t>
+          <t>344146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192111</t>
+          <t>192218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232941</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184137</t>
+          <t>183051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>222804</t>
+          <t>220901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>389224</t>
+          <t>385776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441841</t>
+          <t>441413</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>229279</t>
+          <t>228681</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>270982</t>
+          <t>270905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>241634</t>
+          <t>244502</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>282585</t>
+          <t>282676</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>485357</t>
+          <t>486406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>543215</t>
+          <t>542660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31714</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50598</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>58450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84443</t>
+          <t>84766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18539</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>34262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68226</t>
+          <t>69093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2012 (tasa de respuesta: 99,66%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>44048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63679</t>
+          <t>63781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85740</t>
+          <t>85359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63379</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,47 +3933,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>16657</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11463</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24128</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>19,62%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>13,5%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16657</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11321</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23956</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147005</t>
+          <t>148095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179025</t>
+          <t>180170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156873</t>
+          <t>157348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192490</t>
+          <t>193791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314749</t>
+          <t>313310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>364499</t>
+          <t>359796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141553</t>
+          <t>144195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174973</t>
+          <t>177277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159985</t>
+          <t>160406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>194802</t>
+          <t>196287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309328</t>
+          <t>312771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359027</t>
+          <t>359589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74591</t>
+          <t>74681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>101250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69621</t>
+          <t>69428</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97310</t>
+          <t>97815</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>151353</t>
+          <t>152791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>190825</t>
+          <t>191148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54043</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>59843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80474</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41352</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106726</t>
+          <t>105808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135033</t>
+          <t>133845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>40390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60959</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55699</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76197</t>
+          <t>75933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102162</t>
+          <t>101860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>131302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>56470</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80144</t>
+          <t>80287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>248148</t>
+          <t>249399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288307</t>
+          <t>292892</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241810</t>
+          <t>240792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284560</t>
+          <t>285681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>503545</t>
+          <t>504701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>561173</t>
+          <t>563849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216803</t>
+          <t>216620</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>257248</t>
+          <t>257393</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>244679</t>
+          <t>246340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>287549</t>
+          <t>288682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>475800</t>
+          <t>474574</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533094</t>
+          <t>534169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119133</t>
+          <t>117337</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>153827</t>
+          <t>153101</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>120578</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>153815</t>
+          <t>154662</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>248708</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>296687</t>
+          <t>296882</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49393</t>
+          <t>48844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52391</t>
+          <t>52144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>78987</t>
+          <t>78974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29158</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>42499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>60163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44060</t>
+          <t>43471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61634</t>
+          <t>61457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181707</t>
+          <t>183516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216564</t>
+          <t>217697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174677</t>
+          <t>177575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211622</t>
+          <t>212733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369931</t>
+          <t>369057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>419377</t>
+          <t>418017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>136956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169695</t>
+          <t>167495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169462</t>
+          <t>168710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>205484</t>
+          <t>205469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314095</t>
+          <t>315374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362853</t>
+          <t>363431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63848</t>
+          <t>64868</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91623</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>61141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87588</t>
+          <t>86951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132566</t>
+          <t>131707</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169177</t>
+          <t>169614</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38306</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30796</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>42214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64044</t>
+          <t>64159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73430</t>
+          <t>73339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93856</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79915</t>
+          <t>80313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102738</t>
+          <t>102828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158867</t>
+          <t>159222</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190528</t>
+          <t>190081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>55707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46624</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>65169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86555</t>
+          <t>87980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>114494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>28231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33589</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>54961</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>289190</t>
+          <t>289028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>330856</t>
+          <t>331981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>284191</t>
+          <t>283558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>329216</t>
+          <t>330620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589725</t>
+          <t>589881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>648829</t>
+          <t>652717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195679</t>
+          <t>196518</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236564</t>
+          <t>235578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>253979</t>
+          <t>254779</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>296341</t>
+          <t>298620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>460727</t>
+          <t>459659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>521830</t>
+          <t>520742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92434</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>124332</t>
+          <t>122114</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>87494</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118798</t>
+          <t>119125</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>188678</t>
+          <t>187301</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>232207</t>
+          <t>233160</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41721</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28249</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93013</t>
+          <t>93371</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>522</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>46462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71041</t>
+          <t>71450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>47501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78206</t>
+          <t>78357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93102</t>
+          <t>91418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118931</t>
+          <t>119308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>29218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35292</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58761</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76423</t>
+          <t>74911</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104199</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76511</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>81806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>145205</t>
+          <t>142664</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>177071</t>
+          <t>180259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57188</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83553</t>
+          <t>83353</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
